--- a/files/input/template.xlsx
+++ b/files/input/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProgramFiles\VM_OS\shared\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8E4CFB-4A90-451E-951E-EC47FB27F444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1677CEA6-B70B-4D2D-B877-1A680458AE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31680" yWindow="2880" windowWidth="38700" windowHeight="15375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="48615" yWindow="1215" windowWidth="19185" windowHeight="17730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="21">
   <si>
     <t>trade_id</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>FiboBot</t>
+  </si>
+  <si>
+    <t>MeanBot</t>
   </si>
 </sst>
 </file>
@@ -209,7 +212,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="18">
     <dxf>
       <border outline="0">
         <bottom style="thin">
@@ -400,6 +403,44 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -414,7 +455,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{68D694CD-92E6-45B3-9118-CF9D8D8F57F6}" name="Table2" displayName="Table2" ref="E24:P30" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{68D694CD-92E6-45B3-9118-CF9D8D8F57F6}" name="Table2" displayName="Table2" ref="E24:P30" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
   <autoFilter ref="E24:P30" xr:uid="{68D694CD-92E6-45B3-9118-CF9D8D8F57F6}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{728F177D-253D-43C0-9D08-1611929D397C}" name="trade_id"/>
@@ -435,7 +476,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FE86F7BC-FC81-4DD6-A8FC-A6D693112099}" name="Table26" displayName="Table26" ref="E5:P11" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FE86F7BC-FC81-4DD6-A8FC-A6D693112099}" name="Table26" displayName="Table26" ref="E5:P11" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="E5:P11" xr:uid="{FE86F7BC-FC81-4DD6-A8FC-A6D693112099}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{E22242C5-FE80-48C9-930E-50866008E382}" name="trade_id"/>
@@ -456,7 +497,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BF1137ED-730D-47DE-9126-2E5228BE5DBF}" name="Table27" displayName="Table27" ref="E41:P48" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BF1137ED-730D-47DE-9126-2E5228BE5DBF}" name="Table27" displayName="Table27" ref="E41:P48" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="E41:P48" xr:uid="{BF1137ED-730D-47DE-9126-2E5228BE5DBF}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{43F6BD0D-9896-4A11-A4EF-1337EE02DDEA}" name="trade_id"/>
@@ -477,7 +518,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CF19F3F2-2B98-4A9C-9D3F-0DC68BB0761E}" name="Table274" displayName="Table274" ref="E62:P69" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CF19F3F2-2B98-4A9C-9D3F-0DC68BB0761E}" name="Table274" displayName="Table274" ref="E62:P69" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="E62:P69" xr:uid="{CF19F3F2-2B98-4A9C-9D3F-0DC68BB0761E}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{CED8C13A-4CD1-41D7-8452-F510512A6571}" name="trade_id"/>
@@ -498,7 +539,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B0683529-6857-4F8F-87DE-F47B05C4B64B}" name="Table2742" displayName="Table2742" ref="E83:P90" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B0683529-6857-4F8F-87DE-F47B05C4B64B}" name="Table2742" displayName="Table2742" ref="E83:P90" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="E83:P90" xr:uid="{B0683529-6857-4F8F-87DE-F47B05C4B64B}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{20CC4563-6EE8-4760-9EF0-26174287EA52}" name="trade_id"/>
@@ -513,6 +554,27 @@
     <tableColumn id="10" xr3:uid="{35685DD2-8547-4331-980D-994D1BD255FA}" name="timestamp"/>
     <tableColumn id="11" xr3:uid="{6ABAF89F-7B3D-45D9-83F8-AF2D2DF68AD8}" name="qty"/>
     <tableColumn id="12" xr3:uid="{00912DE2-5D1E-49AD-AE6C-F04D9D1808AF}" name="amount"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{70A50436-289A-4287-82B1-B17B0CFB977B}" name="Table27428" displayName="Table27428" ref="E101:P108" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+  <autoFilter ref="E101:P108" xr:uid="{70A50436-289A-4287-82B1-B17B0CFB977B}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{74BC6DF2-3608-43B6-93C5-2BBAF91F94E5}" name="trade_id"/>
+    <tableColumn id="2" xr3:uid="{F9E0A76E-3F81-4D52-ACC1-BD9DA9B37EFC}" name="broker_order_id"/>
+    <tableColumn id="3" xr3:uid="{59015C9D-6997-4109-8D52-63030C1A74E9}" name="exchange_order_id"/>
+    <tableColumn id="4" xr3:uid="{4EE0FDE4-B8DA-4EC5-82D4-7E74CD5F17B4}" name="instrument"/>
+    <tableColumn id="5" xr3:uid="{EC043372-7535-46B1-BFAC-6FB4A8EA18C6}" name="instrument_key"/>
+    <tableColumn id="6" xr3:uid="{009D64A9-1AB0-4C5D-BEBC-DE3F906A0E79}" name="side"/>
+    <tableColumn id="7" xr3:uid="{256BF5DC-2538-4CE9-AFA3-92FF55B0C210}" name="entry"/>
+    <tableColumn id="8" xr3:uid="{D409D6AA-1C2B-41E4-9435-C84E5F2D8C59}" name="exit"/>
+    <tableColumn id="9" xr3:uid="{933894D0-4423-48D0-8FA9-87A0D1A33614}" name="trailed"/>
+    <tableColumn id="10" xr3:uid="{A109AAB2-58EB-42EF-AF69-FBC50C227250}" name="timestamp"/>
+    <tableColumn id="11" xr3:uid="{0B6DA395-9A92-484A-9F41-03A970F898DF}" name="qty"/>
+    <tableColumn id="12" xr3:uid="{3F2D226F-0946-4EE2-9E0C-5F6D24E26A54}" name="amount"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -781,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81522B13-2059-4C06-A47E-15A0BC3CF508}">
-  <dimension ref="D3:V99"/>
+  <dimension ref="D3:V118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="21.6640625" customWidth="1"/>
@@ -1415,31 +1477,154 @@
       <c r="O96" s="7"/>
       <c r="P96" s="7"/>
     </row>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E99" s="5" t="s">
+    <row r="99" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E99" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="M99" s="8"/>
+      <c r="N99" s="8"/>
+      <c r="O99" s="8"/>
+      <c r="P99" s="8"/>
+    </row>
+    <row r="101" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E101" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P101" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="O109" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E110" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="7"/>
+      <c r="H111" s="7"/>
+      <c r="I111" s="7"/>
+      <c r="J111" s="7"/>
+      <c r="K111" s="7"/>
+      <c r="L111" s="7"/>
+      <c r="M111" s="7"/>
+      <c r="N111" s="7"/>
+      <c r="O111" s="7"/>
+      <c r="P111" s="7"/>
+    </row>
+    <row r="112" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="7"/>
+      <c r="J112" s="7"/>
+      <c r="K112" s="7"/>
+      <c r="L112" s="7"/>
+      <c r="M112" s="7"/>
+      <c r="N112" s="7"/>
+      <c r="O112" s="7"/>
+      <c r="P112" s="7"/>
+    </row>
+    <row r="113" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="7"/>
+      <c r="J113" s="7"/>
+      <c r="K113" s="7"/>
+      <c r="L113" s="7"/>
+      <c r="M113" s="7"/>
+      <c r="N113" s="7"/>
+      <c r="O113" s="7"/>
+      <c r="P113" s="7"/>
+    </row>
+    <row r="114" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E114" s="7"/>
+      <c r="F114" s="7"/>
+      <c r="G114" s="7"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="7"/>
+      <c r="J114" s="7"/>
+      <c r="K114" s="7"/>
+      <c r="L114" s="7"/>
+      <c r="M114" s="7"/>
+      <c r="N114" s="7"/>
+      <c r="O114" s="7"/>
+      <c r="P114" s="7"/>
+    </row>
+    <row r="118" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E118" s="5" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="E99:P99"/>
+    <mergeCell ref="E111:P114"/>
+    <mergeCell ref="E93:P96"/>
+    <mergeCell ref="E60:P60"/>
+    <mergeCell ref="E74:P77"/>
+    <mergeCell ref="E39:P39"/>
+    <mergeCell ref="E53:P56"/>
     <mergeCell ref="E3:P3"/>
     <mergeCell ref="E15:P18"/>
     <mergeCell ref="E22:P22"/>
     <mergeCell ref="E34:P37"/>
     <mergeCell ref="E81:P81"/>
-    <mergeCell ref="E93:P96"/>
-    <mergeCell ref="E60:P60"/>
-    <mergeCell ref="E74:P77"/>
-    <mergeCell ref="E39:P39"/>
-    <mergeCell ref="E53:P56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="5">
+  <tableParts count="6">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>